--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125565383</v>
+        <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,21 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604000</v>
+        <v>603788</v>
       </c>
       <c r="R2" t="n">
-        <v>6936964</v>
+        <v>6936929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125571869</v>
+        <v>125565383</v>
       </c>
       <c r="B3" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603685</v>
+        <v>604000</v>
       </c>
       <c r="R3" t="n">
-        <v>6936888</v>
+        <v>6936964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125560256</v>
+        <v>125571869</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603788</v>
+        <v>603685</v>
       </c>
       <c r="R4" t="n">
-        <v>6936929</v>
+        <v>6936888</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,55 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125565383</v>
+        <v>125571869</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Rödmyran, Mpd</t>
+          <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604000</v>
+        <v>603685</v>
       </c>
       <c r="R3" t="n">
-        <v>6936964</v>
+        <v>6936888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,55 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125571869</v>
+        <v>125565383</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603685</v>
+        <v>604000</v>
       </c>
       <c r="R4" t="n">
-        <v>6936888</v>
+        <v>6936964</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125571869</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125565383</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57649</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125560256</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>125565383</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>125565383</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125560256</v>
+        <v>125560846</v>
       </c>
       <c r="B2" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödmyrhamrarna, Mpd</t>
+          <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603788</v>
+        <v>604052</v>
       </c>
       <c r="R2" t="n">
-        <v>6936929</v>
+        <v>6936962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125571869</v>
+        <v>125560256</v>
       </c>
       <c r="B3" t="n">
-        <v>56844</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603685</v>
+        <v>603788</v>
       </c>
       <c r="R3" t="n">
-        <v>6936888</v>
+        <v>6936929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125565383</v>
+        <v>125565330</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604000</v>
+        <v>604005</v>
       </c>
       <c r="R4" t="n">
-        <v>6936964</v>
+        <v>6936979</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +973,322 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125565383</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>604000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6936964</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125566395</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>603942</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6936844</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125571869</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rödmyrhamrarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603685</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6936888</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24392-2025 artfynd.xlsx
+++ b/artfynd/A 24392-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125560846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125560256</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565330</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565383</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125566395</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,8 +1319,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571869</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>